--- a/artfynd/A 16742-2025 artfynd.xlsx
+++ b/artfynd/A 16742-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125325902</v>
+        <v>125335545</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,21 +715,25 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ringhack tall tretåig hackspett, Vrm</t>
+          <t>Talltita, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337367</v>
+        <v>337335</v>
       </c>
       <c r="R2" t="n">
-        <v>6611231</v>
+        <v>6611125</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Flög från högstubbe björk som visade inhack. Bobygge? Varningsläten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125325736</v>
+        <v>125335997</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,45 +820,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Talltita, Vrm</t>
+          <t>ringhack tall tretåig hackspett, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337314</v>
+        <v>337366</v>
       </c>
       <c r="R3" t="n">
-        <v>6611144</v>
+        <v>6611221</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flög från högstubbe björk som den förmodligen bohackade. Varningsläten.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 16742-2025 artfynd.xlsx
+++ b/artfynd/A 16742-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125335545</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>125335997</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 16742-2025 artfynd.xlsx
+++ b/artfynd/A 16742-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125335545</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,12 +802,7 @@
         <v>125335997</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16742-2025 artfynd.xlsx
+++ b/artfynd/A 16742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125335545</v>
+        <v>125335997</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Talltita, Vrm</t>
+          <t>ringhack tall tretåig hackspett, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337335</v>
+        <v>337366</v>
       </c>
       <c r="R2" t="n">
-        <v>6611125</v>
+        <v>6611221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flög från högstubbe björk som visade inhack. Bobygge? Varningsläten</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,52 +791,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125335997</v>
+        <v>125603948</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ringhack tall tretåig hackspett, Vrm</t>
+          <t>Salstenen, Årstad, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337366</v>
+        <v>337342</v>
       </c>
       <c r="R3" t="n">
-        <v>6611221</v>
+        <v>6611107</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Eda</t>
+          <t>Årjäng</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -863,32 +859,32 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Järnskog</t>
+          <t>Karlanda</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>uppflog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,6 +908,249 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125335545</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Talltita, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>337335</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög från högstubbe björk som visade inhack. Bobygge? Varningsläten</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125603887</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Salstenen, Årstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Schulin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16742-2025 artfynd.xlsx
+++ b/artfynd/A 16742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125335997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125603948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125335545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,8 +1171,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125603887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>